--- a/tools/importer/reports/import-magazine-landing.report.xlsx
+++ b/tools/importer/reports/import-magazine-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-17T03:52:09.704Z</t>
+    <t>2026-09-25T06:43:10.150Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -136,7 +136,7 @@
     <t>magazine-landing</t>
   </si>
   <si>
-    <t>2026-09-24T19:32:44.086Z</t>
+    <t>2026-09-25T06:43:15.305Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -157,7 +157,7 @@
     <t>adventures</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:21.610Z</t>
+    <t>2026-09-24T20:55:20.353Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -172,7 +172,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:26.368Z</t>
+    <t>2026-09-24T20:55:27.760Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -187,7 +187,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:33.082Z</t>
+    <t>2026-09-24T20:55:33.651Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -202,7 +202,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:39.159Z</t>
+    <t>2026-09-24T20:55:39.862Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -217,7 +217,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:43.820Z</t>
+    <t>2026-09-24T20:55:47.218Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -232,7 +232,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:49.271Z</t>
+    <t>2026-09-24T20:55:52.382Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -247,7 +247,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:54.492Z</t>
+    <t>2026-09-24T20:55:58.521Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -262,7 +262,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-09-24T17:43:59.547Z</t>
+    <t>2026-09-24T20:56:04.450Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -277,7 +277,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:03.788Z</t>
+    <t>2026-09-24T20:56:11.301Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -292,7 +292,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:09.511Z</t>
+    <t>2026-09-24T20:56:17.178Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -307,7 +307,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:14.698Z</t>
+    <t>2026-09-24T20:56:22.458Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -322,7 +322,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:18.859Z</t>
+    <t>2026-09-24T20:56:28.873Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -337,7 +337,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:24.577Z</t>
+    <t>2026-09-24T20:56:34.911Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -352,7 +352,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:30.024Z</t>
+    <t>2026-09-24T20:56:41.755Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -367,7 +367,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:34.938Z</t>
+    <t>2026-09-24T20:56:47.576Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -382,7 +382,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-24T17:44:40.162Z</t>
+    <t>2026-09-24T20:56:53.562Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -394,7 +394,7 @@
     <t>us/en/magazine/arctic-surfing.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>["author-bio"]</t>
   </si>
   <si>
     <t>us/en/magazine/arctic-surfing</t>
@@ -403,7 +403,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-09-21T11:55:38.776Z</t>
+    <t>2026-09-24T20:31:52.399Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -418,7 +418,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-21T11:55:44.855Z</t>
+    <t>2026-09-24T20:31:58.028Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -433,7 +433,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-21T11:55:49.625Z</t>
+    <t>2026-09-24T20:32:03.344Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -448,7 +448,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-21T11:55:53.385Z</t>
+    <t>2026-09-24T20:32:07.802Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -463,7 +463,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-21T11:55:59.230Z</t>
+    <t>2026-09-24T20:32:13.362Z</t>
   </si>
   <si>
     <t>Western Australia</t>
